--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-12-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_02-12-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£20.30</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.tradeinsulations.co.uk/product/70mm-celotex/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.176); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff6bdcca235
-	0x7ff6bda22630
-	0x7ff6bd7b16dd
-	0x7ff6bd80a27e
-	0x7ff6bd80a58c
-	0x7ff6bd85ed77
-	0x7ff6bd85baba
-	0x7ff6bd7fb0ed
-	0x7ff6bd7fbf63
-	0x7ff6bdcf5d60
-	0x7ff6bdcefe8a
-	0x7ff6bdd11005
-	0x7ff6bda3d71e
-	0x7ff6bda44e1f
-	0x7ff6bda2b7c4
-	0x7ff6bda2b97f
-	0x7ff6bda118e8
+	0x7ff654c8a235
+	0x7ff6549e2630
+	0x7ff6547716dd
+	0x7ff6547ca27e
+	0x7ff6547ca58c
+	0x7ff65481ed77
+	0x7ff65481baba
+	0x7ff6547bb0ed
+	0x7ff6547bbf63
+	0x7ff654cb5d60
+	0x7ff654cafe8a
+	0x7ff654cd1005
+	0x7ff6549fd71e
+	0x7ff654a04e1f
+	0x7ff6549eb7c4
+	0x7ff6549eb97f
+	0x7ff6549d18e8
 	0x7ffbc9e9e8d7
 	0x7ffbcbf8c53c
 </t>
